--- a/data/00406A_20260731.xlsx
+++ b/data/00406A_20260731.xlsx
@@ -34,16 +34,16 @@
     <x:t>基金每單位淨值(台幣)</x:t>
   </x:si>
   <x:si>
-    <x:t>2026/08/03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15,712,136,172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,777,062,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.84</x:t>
+    <x:t>2026/07/31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,174,089,263</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,789,062,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.48</x:t>
   </x:si>
   <x:si>
     <x:t>序號</x:t>
@@ -76,7 +76,7 @@
     <x:t>610,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>9.23</x:t>
+    <x:t>9.74</x:t>
   </x:si>
   <x:si>
     <x:t>2383</x:t>
@@ -91,7 +91,7 @@
     <x:t>219,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>6.94</x:t>
+    <x:t>6.85</x:t>
   </x:si>
   <x:si>
     <x:t>2454</x:t>
@@ -106,7 +106,7 @@
     <x:t>224,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>5.57</x:t>
+    <x:t>5.25</x:t>
   </x:si>
   <x:si>
     <x:t>3017</x:t>
@@ -121,7 +121,7 @@
     <x:t>297,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>4.82</x:t>
+    <x:t>4.54</x:t>
   </x:si>
   <x:si>
     <x:t>6223</x:t>
@@ -136,7 +136,7 @@
     <x:t>129,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>4.77</x:t>
+    <x:t>4.49</x:t>
   </x:si>
   <x:si>
     <x:t>2345</x:t>
@@ -151,7 +151,7 @@
     <x:t>303,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>4.50</x:t>
+    <x:t>4.24</x:t>
   </x:si>
   <x:si>
     <x:t>3037</x:t>
@@ -166,7 +166,7 @@
     <x:t>781,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>4.30</x:t>
+    <x:t>4.05</x:t>
   </x:si>
   <x:si>
     <x:t>6669</x:t>
@@ -181,7 +181,7 @@
     <x:t>83,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>3.13</x:t>
+    <x:t>2.95</x:t>
   </x:si>
   <x:si>
     <x:t>3665</x:t>
@@ -196,7 +196,7 @@
     <x:t>202,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>2.69</x:t>
+    <x:t>2.80</x:t>
   </x:si>
   <x:si>
     <x:t>8046</x:t>
@@ -214,6 +214,21 @@
     <x:t>2.62</x:t>
   </x:si>
   <x:si>
+    <x:t>2308</x:t>
+  </x:si>
+  <x:si>
+    <x:t>台達電子工業</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Delta Electronics, Inc.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>222,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.40</x:t>
+  </x:si>
+  <x:si>
     <x:t>3711</x:t>
   </x:si>
   <x:si>
@@ -226,7 +241,7 @@
     <x:t>626,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>2.43</x:t>
+    <x:t>2.29</x:t>
   </x:si>
   <x:si>
     <x:t>6274</x:t>
@@ -241,22 +256,7 @@
     <x:t>298,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>2.31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2308</x:t>
-  </x:si>
-  <x:si>
-    <x:t>台達電子工業</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Delta Electronics, Inc.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>222,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.23</x:t>
+    <x:t>2.18</x:t>
   </x:si>
   <x:si>
     <x:t>2303</x:t>
@@ -268,10 +268,10 @@
     <x:t>United Microelectronics Co.,</x:t>
   </x:si>
   <x:si>
-    <x:t>2,650,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.99</x:t>
+    <x:t>2,400,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.91</x:t>
   </x:si>
   <x:si>
     <x:t>2059</x:t>
@@ -286,7 +286,7 @@
     <x:t>29,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>1.59</x:t>
+    <x:t>1.50</x:t>
   </x:si>
   <x:si>
     <x:t>3653</x:t>
@@ -301,7 +301,7 @@
     <x:t>65,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>1.56</x:t>
+    <x:t>1.48</x:t>
   </x:si>
   <x:si>
     <x:t>5274</x:t>
@@ -316,7 +316,22 @@
     <x:t>14,800.00</x:t>
   </x:si>
   <x:si>
-    <x:t>1.50</x:t>
+    <x:t>1.42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2886</x:t>
+  </x:si>
+  <x:si>
+    <x:t>兆豐金融控股</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mega Financial Holding Co.,Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,800,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.33</x:t>
   </x:si>
   <x:si>
     <x:t>2327</x:t>
@@ -331,19 +346,7 @@
     <x:t>356,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>1.25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2886</x:t>
-  </x:si>
-  <x:si>
-    <x:t>兆豐金融控股</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mega Financial Holding Co.,Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,800,000.00</x:t>
+    <x:t>1.18</x:t>
   </x:si>
   <x:si>
     <x:t>7769</x:t>
@@ -355,9 +358,6 @@
     <x:t>Hon.Precision Inc.</x:t>
   </x:si>
   <x:si>
-    <x:t>1.19</x:t>
-  </x:si>
-  <x:si>
     <x:t>3583</x:t>
   </x:si>
   <x:si>
@@ -385,7 +385,7 @@
     <x:t>799,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>1.05</x:t>
+    <x:t>0.99</x:t>
   </x:si>
   <x:si>
     <x:t>2885</x:t>
@@ -400,7 +400,16 @@
     <x:t>2,200,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.95</x:t>
+    <x:t>2360</x:t>
+  </x:si>
+  <x:si>
+    <x:t>致茂電子</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Chroma Ate Inc.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.90</x:t>
   </x:si>
   <x:si>
     <x:t>3443</x:t>
@@ -415,19 +424,7 @@
     <x:t>34,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2360</x:t>
-  </x:si>
-  <x:si>
-    <x:t>致茂電子</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Chroma Ate Inc.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.81</x:t>
+    <x:t>0.85</x:t>
   </x:si>
   <x:si>
     <x:t>3189</x:t>
@@ -442,7 +439,7 @@
     <x:t>178,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.79</x:t>
+    <x:t>0.74</x:t>
   </x:si>
   <x:si>
     <x:t>6139</x:t>
@@ -457,7 +454,22 @@
     <x:t>134,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.65</x:t>
+    <x:t>0.62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4958</x:t>
+  </x:si>
+  <x:si>
+    <x:t>臻鼎科技控股</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Zhen Ding Technology Holding L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>217,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.59</x:t>
   </x:si>
   <x:si>
     <x:t>2344</x:t>
@@ -472,24 +484,6 @@
     <x:t>688,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4958</x:t>
-  </x:si>
-  <x:si>
-    <x:t>臻鼎科技控股</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Zhen Ding Technology Holding L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>217,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.58</x:t>
-  </x:si>
-  <x:si>
     <x:t>6488</x:t>
   </x:si>
   <x:si>
@@ -502,7 +496,22 @@
     <x:t>95,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.52</x:t>
+    <x:t>0.54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2368</x:t>
+  </x:si>
+  <x:si>
+    <x:t>金像電子</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gold Circuit Electronics Ltd.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>97,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.51</x:t>
   </x:si>
   <x:si>
     <x:t>6515</x:t>
@@ -517,6 +526,9 @@
     <x:t>13,000.00</x:t>
   </x:si>
   <x:si>
+    <x:t>0.50</x:t>
+  </x:si>
+  <x:si>
     <x:t>6285</x:t>
   </x:si>
   <x:si>
@@ -529,7 +541,34 @@
     <x:t>323,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.49</x:t>
+    <x:t>0.47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1326</x:t>
+  </x:si>
+  <x:si>
+    <x:t>台灣化學纖維</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Formosa Chemicals &amp; Fiber Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,200,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2395</x:t>
+  </x:si>
+  <x:si>
+    <x:t>研華</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Advantech Co., Ltd.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>121,000.00</x:t>
   </x:si>
   <x:si>
     <x:t>6187</x:t>
@@ -544,36 +583,6 @@
     <x:t>70,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2395</x:t>
-  </x:si>
-  <x:si>
-    <x:t>研華</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Advantech Co., Ltd.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>121,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1326</x:t>
-  </x:si>
-  <x:si>
-    <x:t>台灣化學纖維</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Formosa Chemicals &amp; Fiber Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,200,000.00</x:t>
-  </x:si>
-  <x:si>
     <x:t>0.43</x:t>
   </x:si>
   <x:si>
@@ -589,7 +598,7 @@
     <x:t>395,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.41</x:t>
+    <x:t>0.42</x:t>
   </x:si>
   <x:si>
     <x:t>6805</x:t>
@@ -604,6 +613,9 @@
     <x:t>44,000.00</x:t>
   </x:si>
   <x:si>
+    <x:t>0.39</x:t>
+  </x:si>
+  <x:si>
     <x:t>8996</x:t>
   </x:si>
   <x:si>
@@ -616,16 +628,22 @@
     <x:t>60,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2368</x:t>
-  </x:si>
-  <x:si>
-    <x:t>金像電子</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gold Circuit Electronics Ltd.</x:t>
+    <x:t>0.34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2449</x:t>
+  </x:si>
+  <x:si>
+    <x:t>京元電子</x:t>
+  </x:si>
+  <x:si>
+    <x:t>King Yuan Electronics Co., Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>210,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.31</x:t>
   </x:si>
   <x:si>
     <x:t>2455</x:t>
@@ -640,22 +658,7 @@
     <x:t>155,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2449</x:t>
-  </x:si>
-  <x:si>
-    <x:t>京元電子</x:t>
-  </x:si>
-  <x:si>
-    <x:t>King Yuan Electronics Co., Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>210,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.31</x:t>
+    <x:t>0.30</x:t>
   </x:si>
   <x:si>
     <x:t>2472</x:t>
@@ -673,6 +676,36 @@
     <x:t>0.25</x:t>
   </x:si>
   <x:si>
+    <x:t>3167</x:t>
+  </x:si>
+  <x:si>
+    <x:t>大量科技</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ta Liang Technology Co., Ltd.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>71,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5536</x:t>
+  </x:si>
+  <x:si>
+    <x:t>聖暉工程科技</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Acter Co., Ltd.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.22</x:t>
+  </x:si>
+  <x:si>
     <x:t>5289</x:t>
   </x:si>
   <x:si>
@@ -685,22 +718,76 @@
     <x:t>26,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5536</x:t>
-  </x:si>
-  <x:si>
-    <x:t>聖暉工程科技</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Acter Co., Ltd.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.22</x:t>
+    <x:t>8210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>勤誠興業</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Chenbro Micom Co., Ltd.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>禾伸堂企業</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Holy Stone Enterprise Co., Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>漢唐集成</x:t>
+  </x:si>
+  <x:si>
+    <x:t>United Integrated Services Co.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>順達科技</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dynapack Int'l Technology Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100,000.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6196</x:t>
+  </x:si>
+  <x:si>
+    <x:t>帆宣系統科技</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marketech International Corp.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>聯茂電子</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ITEQ Corp.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.17</x:t>
   </x:si>
   <x:si>
     <x:t>8150</x:t>
@@ -712,94 +799,7 @@
     <x:t>ChipMos Tehnologies Inc.</x:t>
   </x:si>
   <x:si>
-    <x:t>455,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>勤誠興業</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Chenbro Micom Co., Ltd.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>漢唐集成</x:t>
-  </x:si>
-  <x:si>
-    <x:t>United Integrated Services Co.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>順達科技</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dynapack Int'l Technology Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6196</x:t>
-  </x:si>
-  <x:si>
-    <x:t>帆宣系統科技</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Marketech International Corp.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>聯茂電子</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ITEQ Corp.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>禾伸堂企業</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Holy Stone Enterprise Co., Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>62,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3167</x:t>
-  </x:si>
-  <x:si>
-    <x:t>大量科技</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ta Liang Technology Co., Ltd.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48,000.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.16</x:t>
+    <x:t>355,000.00</x:t>
   </x:si>
   <x:si>
     <x:t>6683</x:t>
@@ -814,6 +814,21 @@
     <x:t>25,000.00</x:t>
   </x:si>
   <x:si>
+    <x:t>0.15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3533</x:t>
+  </x:si>
+  <x:si>
+    <x:t>嘉澤端子工業</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lotes Co., Ltd.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,000.00</x:t>
+  </x:si>
+  <x:si>
     <x:t>5439</x:t>
   </x:si>
   <x:si>
@@ -826,19 +841,7 @@
     <x:t>110,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3533</x:t>
-  </x:si>
-  <x:si>
-    <x:t>嘉澤端子工業</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lotes Co., Ltd.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12,000.00</x:t>
+    <x:t>0.14</x:t>
   </x:si>
   <x:si>
     <x:t>6138</x:t>
@@ -853,9 +856,6 @@
     <x:t>80,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.14</x:t>
-  </x:si>
-  <x:si>
     <x:t>3357</x:t>
   </x:si>
   <x:si>
@@ -898,7 +898,7 @@
     <x:t>19,000.00</x:t>
   </x:si>
   <x:si>
-    <x:t>0.09</x:t>
+    <x:t>0.08</x:t>
   </x:si>
   <x:si>
     <x:t>期貨代碼</x:t>
@@ -925,7 +925,7 @@
     <x:t>202608</x:t>
   </x:si>
   <x:si>
-    <x:t>22.56</x:t>
+    <x:t>23.63</x:t>
   </x:si>
   <x:si>
     <x:t>商品代碼</x:t>
@@ -949,7 +949,7 @@
     <x:t>-500.00</x:t>
   </x:si>
   <x:si>
-    <x:t>-5.34</x:t>
+    <x:t>-5.65</x:t>
   </x:si>
   <x:si>
     <x:t>TX1</x:t>
@@ -961,7 +961,7 @@
     <x:t>-1,450.00</x:t>
   </x:si>
   <x:si>
-    <x:t>-16.99</x:t>
+    <x:t>-17.39</x:t>
   </x:si>
   <x:si>
     <x:t>項目</x:t>
@@ -979,25 +979,25 @@
     <x:t>TWD</x:t>
   </x:si>
   <x:si>
-    <x:t>1,869,738,737.00 (TWD)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.90</x:t>
+    <x:t>2,567,474,080.00 (TWD)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.92</x:t>
   </x:si>
   <x:si>
     <x:t>保證金</x:t>
   </x:si>
   <x:si>
-    <x:t>1,659,441,020.00 (TWD)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.56</x:t>
+    <x:t>1,701,097,020.00 (TWD)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.21</x:t>
   </x:si>
   <x:si>
     <x:t>應收(付)證券款</x:t>
   </x:si>
   <x:si>
-    <x:t>-35,503,749.00 (TWD)</x:t>
+    <x:t>-738,514,240.00 (TWD)</x:t>
   </x:si>
   <x:si>
     <x:t>0.00</x:t>
@@ -1877,7 +1877,7 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
-        <x:v>105</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6">
@@ -1885,19 +1885,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B29" s="8" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C29" s="8" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D29" s="8" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E29" s="3" t="s">
         <x:v>89</x:v>
       </x:c>
       <x:c r="F29" s="3" t="s">
-        <x:v>113</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
@@ -1957,7 +1957,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="F32" s="3" t="s">
-        <x:v>128</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6">
@@ -1965,19 +1965,19 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B33" s="8" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C33" s="8" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="C33" s="8" t="s">
+      <x:c r="D33" s="8" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="D33" s="8" t="s">
+      <x:c r="E33" s="3" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F33" s="3" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="E33" s="3" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="F33" s="3" t="s">
-        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:6">
@@ -1985,19 +1985,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B34" s="8" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C34" s="8" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D34" s="8" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="C34" s="8" t="s">
+      <x:c r="E34" s="3" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="D34" s="8" t="s">
+      <x:c r="F34" s="3" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="E34" s="3" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F34" s="3" t="s">
-        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:6">
@@ -2005,19 +2005,19 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B35" s="8" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C35" s="8" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="C35" s="8" t="s">
+      <x:c r="D35" s="8" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="D35" s="8" t="s">
+      <x:c r="E35" s="3" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="E35" s="3" t="s">
+      <x:c r="F35" s="3" t="s">
         <x:v>141</x:v>
-      </x:c>
-      <x:c r="F35" s="3" t="s">
-        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:6">
@@ -2025,19 +2025,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B36" s="8" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C36" s="8" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="C36" s="8" t="s">
+      <x:c r="D36" s="8" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="D36" s="8" t="s">
+      <x:c r="E36" s="3" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="E36" s="3" t="s">
+      <x:c r="F36" s="3" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="F36" s="3" t="s">
-        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6">
@@ -2045,19 +2045,19 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B37" s="8" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C37" s="8" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="C37" s="8" t="s">
+      <x:c r="D37" s="8" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="D37" s="8" t="s">
+      <x:c r="E37" s="3" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="E37" s="3" t="s">
+      <x:c r="F37" s="3" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="F37" s="3" t="s">
-        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6">
@@ -2065,19 +2065,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B38" s="8" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C38" s="8" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="C38" s="8" t="s">
+      <x:c r="D38" s="8" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="D38" s="8" t="s">
+      <x:c r="E38" s="3" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="E38" s="3" t="s">
-        <x:v>156</x:v>
-      </x:c>
       <x:c r="F38" s="3" t="s">
-        <x:v>157</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:6">
@@ -2085,19 +2085,19 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B39" s="8" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C39" s="8" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D39" s="8" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="C39" s="8" t="s">
+      <x:c r="E39" s="3" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="D39" s="8" t="s">
+      <x:c r="F39" s="3" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="E39" s="3" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="F39" s="3" t="s">
-        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:6">
@@ -2105,19 +2105,19 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B40" s="8" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C40" s="8" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D40" s="8" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="C40" s="8" t="s">
+      <x:c r="E40" s="3" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="D40" s="8" t="s">
+      <x:c r="F40" s="3" t="s">
         <x:v>165</x:v>
-      </x:c>
-      <x:c r="E40" s="3" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="F40" s="3" t="s">
-        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:6">
@@ -2125,19 +2125,19 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B41" s="8" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C41" s="8" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="C41" s="8" t="s">
+      <x:c r="D41" s="8" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="D41" s="8" t="s">
+      <x:c r="E41" s="3" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="E41" s="3" t="s">
+      <x:c r="F41" s="3" t="s">
         <x:v>170</x:v>
-      </x:c>
-      <x:c r="F41" s="3" t="s">
-        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:6">
@@ -2145,19 +2145,19 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B42" s="8" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="C42" s="8" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="C42" s="8" t="s">
+      <x:c r="D42" s="8" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="D42" s="8" t="s">
+      <x:c r="E42" s="3" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="E42" s="3" t="s">
+      <x:c r="F42" s="3" t="s">
         <x:v>175</x:v>
-      </x:c>
-      <x:c r="F42" s="3" t="s">
-        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:6">
@@ -2165,19 +2165,19 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B43" s="8" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C43" s="8" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="C43" s="8" t="s">
+      <x:c r="D43" s="8" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="D43" s="8" t="s">
+      <x:c r="E43" s="3" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="E43" s="3" t="s">
+      <x:c r="F43" s="3" t="s">
         <x:v>180</x:v>
-      </x:c>
-      <x:c r="F43" s="3" t="s">
-        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:6">
@@ -2185,19 +2185,19 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B44" s="8" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="C44" s="8" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="C44" s="8" t="s">
+      <x:c r="D44" s="8" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="D44" s="8" t="s">
+      <x:c r="E44" s="3" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="E44" s="3" t="s">
-        <x:v>185</x:v>
-      </x:c>
       <x:c r="F44" s="3" t="s">
-        <x:v>186</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:6">
@@ -2205,19 +2205,19 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B45" s="8" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C45" s="8" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D45" s="8" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="C45" s="8" t="s">
+      <x:c r="E45" s="3" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="D45" s="8" t="s">
+      <x:c r="F45" s="3" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="E45" s="3" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="F45" s="3" t="s">
-        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:6">
@@ -2225,19 +2225,19 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B46" s="8" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="C46" s="8" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D46" s="8" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="C46" s="8" t="s">
+      <x:c r="E46" s="3" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="D46" s="8" t="s">
+      <x:c r="F46" s="3" t="s">
         <x:v>194</x:v>
-      </x:c>
-      <x:c r="E46" s="3" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F46" s="3" t="s">
-        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:6">
@@ -2245,19 +2245,19 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B47" s="8" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="C47" s="8" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="C47" s="8" t="s">
+      <x:c r="D47" s="8" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="D47" s="8" t="s">
+      <x:c r="E47" s="3" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="E47" s="3" t="s">
+      <x:c r="F47" s="3" t="s">
         <x:v>199</x:v>
-      </x:c>
-      <x:c r="F47" s="3" t="s">
-        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:6">
@@ -2265,19 +2265,19 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B48" s="8" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="C48" s="8" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="C48" s="8" t="s">
+      <x:c r="D48" s="8" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="D48" s="8" t="s">
+      <x:c r="E48" s="3" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="E48" s="3" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="F48" s="3" t="s">
-        <x:v>200</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:6">
@@ -2285,19 +2285,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B49" s="8" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C49" s="8" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D49" s="8" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E49" s="3" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="F49" s="3" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:6">
@@ -2305,19 +2305,19 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B50" s="8" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C50" s="8" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="D50" s="8" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E50" s="3" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F50" s="3" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:6">
@@ -2325,19 +2325,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B51" s="8" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C51" s="8" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D51" s="8" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E51" s="3" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="F51" s="3" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:6">
@@ -2345,19 +2345,19 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B52" s="8" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C52" s="8" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="D52" s="8" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="E52" s="3" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="F52" s="3" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:6">
@@ -2365,19 +2365,19 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B53" s="8" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C53" s="8" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="D53" s="8" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E53" s="3" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F53" s="3" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:6">
@@ -2385,19 +2385,19 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B54" s="8" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="C54" s="8" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D54" s="8" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="E54" s="3" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="F54" s="3" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="C54" s="8" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="D54" s="8" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="E54" s="3" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="F54" s="3" t="s">
-        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:6">
@@ -2405,19 +2405,19 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B55" s="8" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C55" s="8" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="D55" s="8" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E55" s="3" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="F55" s="3" t="s">
-        <x:v>228</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:6">
@@ -2425,19 +2425,19 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B56" s="8" t="s">
-        <x:v>237</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C56" s="8" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D56" s="8" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="E56" s="3" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="F56" s="3" t="s">
         <x:v>238</x:v>
-      </x:c>
-      <x:c r="D56" s="8" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="E56" s="3" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="F56" s="3" t="s">
-        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:6">
@@ -2445,19 +2445,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B57" s="8" t="s">
-        <x:v>241</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C57" s="8" t="s">
-        <x:v>242</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D57" s="8" t="s">
-        <x:v>243</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E57" s="3" t="s">
-        <x:v>244</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F57" s="3" t="s">
-        <x:v>240</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:6">
@@ -2465,19 +2465,19 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B58" s="8" t="s">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C58" s="8" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D58" s="8" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E58" s="3" t="s">
-        <x:v>199</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="F58" s="3" t="s">
-        <x:v>248</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:6">
@@ -2485,19 +2485,19 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B59" s="8" t="s">
-        <x:v>249</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C59" s="8" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D59" s="8" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="E59" s="3" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F59" s="3" t="s">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="D59" s="8" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="E59" s="3" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="F59" s="3" t="s">
-        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:6">
@@ -2505,19 +2505,19 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B60" s="8" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C60" s="8" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D60" s="8" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E60" s="3" t="s">
-        <x:v>256</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="F60" s="3" t="s">
-        <x:v>252</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:6">
@@ -2525,19 +2525,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B61" s="8" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="C61" s="8" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="D61" s="8" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="E61" s="3" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="F61" s="3" t="s">
         <x:v>257</x:v>
-      </x:c>
-      <x:c r="C61" s="8" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D61" s="8" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="E61" s="3" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="F61" s="3" t="s">
-        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:6">
@@ -2557,7 +2557,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="F62" s="3" t="s">
-        <x:v>261</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:6">
@@ -2565,19 +2565,19 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B63" s="8" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="C63" s="8" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D63" s="8" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="E63" s="3" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="F63" s="3" t="s">
         <x:v>266</x:v>
-      </x:c>
-      <x:c r="C63" s="8" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="D63" s="8" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="E63" s="3" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="F63" s="3" t="s">
-        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:6">
@@ -2597,7 +2597,7 @@
         <x:v>274</x:v>
       </x:c>
       <x:c r="F64" s="3" t="s">
-        <x:v>270</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:6">
@@ -2605,19 +2605,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B65" s="8" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="C65" s="8" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="D65" s="8" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="E65" s="3" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="F65" s="3" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="C65" s="8" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="D65" s="8" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="E65" s="3" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="F65" s="3" t="s">
-        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:6">
